--- a/data/b2_bonsucesso/B2 Bonsucesso 06-2026.xlsx
+++ b/data/b2_bonsucesso/B2 Bonsucesso 06-2026.xlsx
@@ -4748,11 +4748,11 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Manutenção preventiva das bombas</t>
+          <t>Limpeza da caixa separadora</t>
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>2668.72</v>
+        <v>2101.51</v>
       </c>
     </row>
     <row r="3">
@@ -4770,7 +4770,7 @@
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>64957.4</v>
+        <v>64588.51</v>
       </c>
     </row>
     <row r="4">
@@ -4779,52 +4779,52 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Material de limpeza e escritório</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>1280.24</v>
+        <v>3761.65</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>46180</v>
+        <v>46183</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>3984.86</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Uniformes e EPI</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>3600</v>
+        <v>1029.35</v>
       </c>
     </row>
     <row r="7">
@@ -4833,160 +4833,160 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Monitoramento e alarme</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>904.02</v>
+        <v>1403.78</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46185</v>
+        <v>46187</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>1395.48</v>
+        <v>4333.81</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Troca de filtros das bombas</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>2170.35</v>
+        <v>9683.49</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>4088.07</v>
+        <v>1901.34</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Material de limpeza e escritório</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>10182.98</v>
+        <v>1058.26</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46188</v>
+        <v>46193</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>1910.18</v>
+        <v>23019.31</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>23189.71</v>
+        <v>4335.71</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46193</v>
+        <v>46197</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Tarifas bancárias</t>
+          <t>Troca de filtros das bombas</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>2644.01</v>
+        <v>1974.21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>46194</v>
+        <v>46197</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Seguro do posto</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>4395.02</v>
+        <v>886.48</v>
       </c>
     </row>
     <row r="16">
@@ -5004,7 +5004,7 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>3990.42</v>
+        <v>4056.72</v>
       </c>
     </row>
     <row r="17">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>1188.15</v>
+        <v>1194.18</v>
       </c>
     </row>
   </sheetData>
